--- a/Pruebas calificadas/COLEGIO DE LA BICI. DIAGNOSTICA-902_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO DE LA BICI. DIAGNOSTICA-902_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1056,11 +1052,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -1068,7 +1060,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1309,11 +1301,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -1321,7 +1309,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1562,11 +1550,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -1574,7 +1558,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1815,11 +1799,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -1827,7 +1807,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2060,11 +2040,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -2072,7 +2048,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2309,11 +2285,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -2321,7 +2293,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2562,11 +2534,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -2574,7 +2542,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2815,11 +2783,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -2827,7 +2791,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3068,11 +3032,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -3080,7 +3040,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3321,11 +3281,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -3333,7 +3289,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3574,11 +3530,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -3586,7 +3538,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3747,11 +3699,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -3759,7 +3707,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4000,11 +3948,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -4012,7 +3956,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4253,11 +4197,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -4265,7 +4205,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4506,11 +4446,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -4518,7 +4454,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4679,11 +4615,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -4691,7 +4623,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -4932,11 +4864,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -4944,7 +4872,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5105,11 +5033,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -5117,7 +5041,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5358,11 +5282,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -5370,7 +5290,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5531,11 +5451,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -5543,7 +5459,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -5784,11 +5700,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -5796,7 +5708,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6037,11 +5949,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -6049,7 +5957,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6290,11 +6198,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -6302,7 +6206,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6463,11 +6367,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -6475,7 +6375,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -6716,11 +6616,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -6728,7 +6624,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -6969,11 +6865,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -6981,7 +6873,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7222,11 +7114,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -7234,7 +7122,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
